--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawn.hsieh\Desktop\隔熱紙下單小幫手\TMS148測試\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08F99037-7695-402A-9D15-74958DF09F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7201704E-19D1-4454-ACB9-D82305C41F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1605" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="234">
   <si>
     <t>車型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,14 +49,6 @@
   </si>
   <si>
     <t>Stonic</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ceed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1109,68 +1101,68 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="F1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
         <v>30</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>30</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>32</v>
       </c>
       <c r="G3" s="1">
         <v>78</v>
@@ -1178,206 +1170,206 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
         <v>37</v>
       </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
         <v>50</v>
       </c>
-      <c r="C8" t="s">
+      <c r="G8" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="C9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" t="s">
         <v>59</v>
       </c>
-      <c r="C11" t="s">
+      <c r="G11" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G12" s="1">
         <v>75</v>
@@ -1385,68 +1377,68 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" t="s">
         <v>67</v>
       </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="G14" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G15" s="1">
         <v>78</v>
@@ -1454,206 +1446,206 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" t="s">
         <v>78</v>
       </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" t="s">
-        <v>80</v>
-      </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>66</v>
+      </c>
+      <c r="E23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D23" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G24" s="1">
         <v>75</v>
@@ -1661,68 +1653,68 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
         <v>66</v>
       </c>
-      <c r="D25" t="s">
-        <v>68</v>
-      </c>
       <c r="E25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
         <v>27</v>
       </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>29</v>
-      </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F26" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G27" s="1">
         <v>78</v>
@@ -1730,137 +1722,137 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" t="s">
+        <v>40</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D29" t="s">
-        <v>85</v>
-      </c>
-      <c r="E29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F29" t="s">
-        <v>42</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D30" t="s">
-        <v>85</v>
-      </c>
-      <c r="E30" t="s">
-        <v>31</v>
-      </c>
-      <c r="F30" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F31" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D32" t="s">
-        <v>85</v>
-      </c>
-      <c r="E32" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" t="s">
-        <v>61</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G33" s="1">
         <v>75</v>
@@ -1868,45 +1860,45 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" t="s">
         <v>27</v>
       </c>
-      <c r="B34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" t="s">
-        <v>29</v>
-      </c>
       <c r="D34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" t="s">
+        <v>67</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="F34" t="s">
-        <v>69</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F35" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G35" s="1">
         <v>78</v>
@@ -1914,206 +1906,206 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F36" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37" t="s">
+        <v>40</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D37" t="s">
-        <v>94</v>
-      </c>
-      <c r="E37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" t="s">
-        <v>42</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="D38" t="s">
-        <v>94</v>
-      </c>
-      <c r="E38" t="s">
-        <v>36</v>
-      </c>
-      <c r="F38" t="s">
-        <v>42</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C40" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40" t="s">
+        <v>74</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D40" t="s">
-        <v>94</v>
-      </c>
-      <c r="E40" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" t="s">
-        <v>76</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E41" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F41" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D42" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F42" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" t="s">
+        <v>29</v>
+      </c>
+      <c r="F43" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="D43" t="s">
-        <v>104</v>
-      </c>
-      <c r="E43" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" t="s">
-        <v>61</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D44" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E44" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F44" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G44" s="1">
         <v>75</v>
@@ -2121,68 +2113,68 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D45" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F45" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" t="s">
         <v>107</v>
       </c>
-      <c r="B46" t="s">
+      <c r="D46" t="s">
         <v>108</v>
       </c>
-      <c r="C46" t="s">
+      <c r="E46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46" t="s">
         <v>109</v>
       </c>
-      <c r="D46" t="s">
+      <c r="G46" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="E46" t="s">
-        <v>31</v>
-      </c>
-      <c r="F46" t="s">
-        <v>111</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D47" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E47" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F47" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G47" s="1">
         <v>75</v>
@@ -2190,91 +2182,91 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B48" t="s">
+        <v>113</v>
+      </c>
+      <c r="C48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" t="s">
+        <v>108</v>
+      </c>
+      <c r="E48" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48" t="s">
         <v>115</v>
       </c>
-      <c r="C48" t="s">
+      <c r="G48" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="D48" t="s">
-        <v>110</v>
-      </c>
-      <c r="E48" t="s">
-        <v>31</v>
-      </c>
-      <c r="F48" t="s">
-        <v>117</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" t="s">
+        <v>118</v>
+      </c>
+      <c r="C49" t="s">
         <v>119</v>
       </c>
-      <c r="B49" t="s">
+      <c r="D49" t="s">
+        <v>108</v>
+      </c>
+      <c r="E49" t="s">
+        <v>34</v>
+      </c>
+      <c r="F49" t="s">
+        <v>115</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C49" t="s">
-        <v>121</v>
-      </c>
-      <c r="D49" t="s">
-        <v>110</v>
-      </c>
-      <c r="E49" t="s">
-        <v>36</v>
-      </c>
-      <c r="F49" t="s">
-        <v>117</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B50" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" t="s">
+        <v>122</v>
+      </c>
+      <c r="D50" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" t="s">
         <v>123</v>
       </c>
-      <c r="C50" t="s">
+      <c r="G50" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="D50" t="s">
-        <v>85</v>
-      </c>
-      <c r="E50" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" t="s">
-        <v>125</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D51" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E51" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F51" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G51" s="1">
         <v>70</v>
@@ -2282,45 +2274,45 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C52" t="s">
+        <v>122</v>
+      </c>
+      <c r="D52" t="s">
+        <v>128</v>
+      </c>
+      <c r="E52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" t="s">
+        <v>123</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="D52" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" t="s">
-        <v>31</v>
-      </c>
-      <c r="F52" t="s">
-        <v>125</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
+        <v>126</v>
+      </c>
+      <c r="D53" t="s">
         <v>128</v>
       </c>
-      <c r="D53" t="s">
-        <v>130</v>
-      </c>
       <c r="E53" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F53" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G53" s="1">
         <v>70</v>
@@ -2328,45 +2320,45 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C54" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" t="s">
+        <v>128</v>
+      </c>
+      <c r="E54" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54" t="s">
         <v>109</v>
       </c>
-      <c r="D54" t="s">
-        <v>130</v>
-      </c>
-      <c r="E54" t="s">
-        <v>31</v>
-      </c>
-      <c r="F54" t="s">
-        <v>111</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E55" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G55" s="1">
         <v>75</v>
@@ -2374,91 +2366,91 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B56" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C56" t="s">
+        <v>114</v>
+      </c>
+      <c r="D56" t="s">
+        <v>128</v>
+      </c>
+      <c r="E56" t="s">
+        <v>29</v>
+      </c>
+      <c r="F56" t="s">
+        <v>115</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="D56" t="s">
-        <v>130</v>
-      </c>
-      <c r="E56" t="s">
-        <v>31</v>
-      </c>
-      <c r="F56" t="s">
-        <v>117</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>117</v>
+      </c>
+      <c r="B57" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" t="s">
         <v>119</v>
       </c>
-      <c r="B57" t="s">
-        <v>135</v>
-      </c>
-      <c r="C57" t="s">
-        <v>121</v>
-      </c>
       <c r="D57" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E57" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F57" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B58" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
+        <v>122</v>
+      </c>
+      <c r="D58" t="s">
+        <v>135</v>
+      </c>
+      <c r="E58" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58" t="s">
+        <v>123</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="D58" t="s">
-        <v>137</v>
-      </c>
-      <c r="E58" t="s">
-        <v>31</v>
-      </c>
-      <c r="F58" t="s">
-        <v>125</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C59" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D59" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E59" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F59" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G59" s="1">
         <v>70</v>
@@ -2466,68 +2458,68 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C60" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D60" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E60" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F60" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B61" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C61" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" t="s">
+        <v>135</v>
+      </c>
+      <c r="E61" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61" t="s">
         <v>109</v>
       </c>
-      <c r="D61" t="s">
-        <v>137</v>
-      </c>
-      <c r="E61" t="s">
-        <v>31</v>
-      </c>
-      <c r="F61" t="s">
-        <v>111</v>
-      </c>
       <c r="G61" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B62" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C62" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F62" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G62" s="1">
         <v>75</v>
@@ -2535,137 +2527,137 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B63" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C63" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D63" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E63" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F63" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C64" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" t="s">
+        <v>135</v>
+      </c>
+      <c r="E64" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64" t="s">
+        <v>115</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="D64" t="s">
-        <v>137</v>
-      </c>
-      <c r="E64" t="s">
-        <v>31</v>
-      </c>
-      <c r="F64" t="s">
-        <v>117</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>117</v>
+      </c>
+      <c r="B65" t="s">
+        <v>144</v>
+      </c>
+      <c r="C65" t="s">
         <v>119</v>
       </c>
-      <c r="B65" t="s">
-        <v>146</v>
-      </c>
-      <c r="C65" t="s">
-        <v>121</v>
-      </c>
       <c r="D65" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E65" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F65" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B66" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C66" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E66" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F66" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B67" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C67" t="s">
+        <v>122</v>
+      </c>
+      <c r="D67" t="s">
+        <v>148</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67" t="s">
+        <v>123</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="D67" t="s">
-        <v>150</v>
-      </c>
-      <c r="E67" t="s">
-        <v>31</v>
-      </c>
-      <c r="F67" t="s">
-        <v>125</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B68" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C68" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D68" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E68" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F68" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G68" s="1">
         <v>70</v>
@@ -2673,68 +2665,68 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B69" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C69" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D69" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E69" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F69" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B70" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C70" t="s">
+        <v>107</v>
+      </c>
+      <c r="D70" t="s">
+        <v>148</v>
+      </c>
+      <c r="E70" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70" t="s">
         <v>109</v>
       </c>
-      <c r="D70" t="s">
-        <v>150</v>
-      </c>
-      <c r="E70" t="s">
-        <v>31</v>
-      </c>
-      <c r="F70" t="s">
-        <v>111</v>
-      </c>
       <c r="G70" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B71" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C71" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D71" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E71" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F71" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G71" s="1">
         <v>75</v>
@@ -2742,137 +2734,137 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B72" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C72" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D72" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E72" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F72" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B73" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C73" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" t="s">
+        <v>148</v>
+      </c>
+      <c r="E73" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73" t="s">
+        <v>115</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="D73" t="s">
-        <v>150</v>
-      </c>
-      <c r="E73" t="s">
-        <v>31</v>
-      </c>
-      <c r="F73" t="s">
-        <v>117</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>117</v>
+      </c>
+      <c r="B74" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" t="s">
         <v>119</v>
       </c>
-      <c r="B74" t="s">
-        <v>157</v>
-      </c>
-      <c r="C74" t="s">
-        <v>121</v>
-      </c>
       <c r="D74" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E74" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F74" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B75" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C75" t="s">
+        <v>146</v>
+      </c>
+      <c r="D75" t="s">
         <v>148</v>
       </c>
-      <c r="D75" t="s">
-        <v>150</v>
-      </c>
       <c r="E75" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F75" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B76" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C76" t="s">
+        <v>122</v>
+      </c>
+      <c r="D76" t="s">
+        <v>66</v>
+      </c>
+      <c r="E76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76" t="s">
+        <v>123</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>124</v>
-      </c>
-      <c r="D76" t="s">
-        <v>68</v>
-      </c>
-      <c r="E76" t="s">
-        <v>31</v>
-      </c>
-      <c r="F76" t="s">
-        <v>125</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C77" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D77" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E77" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F77" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G77" s="1">
         <v>70</v>
@@ -2880,68 +2872,68 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C78" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D78" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E78" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F78" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B79" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C79" t="s">
+        <v>107</v>
+      </c>
+      <c r="D79" t="s">
+        <v>66</v>
+      </c>
+      <c r="E79" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79" t="s">
         <v>109</v>
       </c>
-      <c r="D79" t="s">
-        <v>68</v>
-      </c>
-      <c r="E79" t="s">
-        <v>31</v>
-      </c>
-      <c r="F79" t="s">
-        <v>111</v>
-      </c>
       <c r="G79" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B80" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C80" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D80" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E80" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F80" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G80" s="1">
         <v>75</v>
@@ -2949,114 +2941,114 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B81" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C81" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D81" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F81" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B82" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C82" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" t="s">
+        <v>66</v>
+      </c>
+      <c r="E82" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82" t="s">
+        <v>115</v>
+      </c>
+      <c r="G82" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="D82" t="s">
-        <v>68</v>
-      </c>
-      <c r="E82" t="s">
-        <v>31</v>
-      </c>
-      <c r="F82" t="s">
-        <v>117</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>117</v>
+      </c>
+      <c r="B83" t="s">
+        <v>164</v>
+      </c>
+      <c r="C83" t="s">
         <v>119</v>
       </c>
-      <c r="B83" t="s">
-        <v>166</v>
-      </c>
-      <c r="C83" t="s">
-        <v>121</v>
-      </c>
       <c r="D83" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E83" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F83" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B84" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C84" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D84" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E84" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
+        <v>166</v>
+      </c>
+      <c r="B85" t="s">
+        <v>167</v>
+      </c>
+      <c r="C85" t="s">
         <v>168</v>
       </c>
-      <c r="B85" t="s">
+      <c r="D85" t="s">
+        <v>28</v>
+      </c>
+      <c r="E85" t="s">
+        <v>34</v>
+      </c>
+      <c r="F85" t="s">
         <v>169</v>
-      </c>
-      <c r="C85" t="s">
-        <v>170</v>
-      </c>
-      <c r="D85" t="s">
-        <v>30</v>
-      </c>
-      <c r="E85" t="s">
-        <v>36</v>
-      </c>
-      <c r="F85" t="s">
-        <v>171</v>
       </c>
       <c r="G85" s="1">
         <v>70</v>
@@ -3064,68 +3056,68 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B86" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" t="s">
+        <v>171</v>
+      </c>
+      <c r="D86" t="s">
+        <v>28</v>
+      </c>
+      <c r="E86" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86" t="s">
+        <v>169</v>
+      </c>
+      <c r="G86" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="C86" t="s">
-        <v>173</v>
-      </c>
-      <c r="D86" t="s">
-        <v>30</v>
-      </c>
-      <c r="E86" t="s">
-        <v>31</v>
-      </c>
-      <c r="F86" t="s">
-        <v>171</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C87" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D87" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E87" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F87" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
+        <v>175</v>
+      </c>
+      <c r="C88" t="s">
+        <v>176</v>
+      </c>
+      <c r="D88" t="s">
+        <v>28</v>
+      </c>
+      <c r="E88" t="s">
         <v>177</v>
       </c>
-      <c r="C88" t="s">
+      <c r="F88" t="s">
         <v>178</v>
-      </c>
-      <c r="D88" t="s">
-        <v>30</v>
-      </c>
-      <c r="E88" t="s">
-        <v>179</v>
-      </c>
-      <c r="F88" t="s">
-        <v>180</v>
       </c>
       <c r="G88" s="1">
         <v>70</v>
@@ -3133,68 +3125,68 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B89" t="s">
+        <v>179</v>
+      </c>
+      <c r="C89" t="s">
+        <v>180</v>
+      </c>
+      <c r="D89" t="s">
+        <v>28</v>
+      </c>
+      <c r="E89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F89" t="s">
+        <v>178</v>
+      </c>
+      <c r="G89" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="C89" t="s">
-        <v>182</v>
-      </c>
-      <c r="D89" t="s">
-        <v>30</v>
-      </c>
-      <c r="E89" t="s">
-        <v>31</v>
-      </c>
-      <c r="F89" t="s">
-        <v>180</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B90" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C90" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D90" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E90" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F90" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B91" t="s">
+        <v>184</v>
+      </c>
+      <c r="C91" t="s">
+        <v>185</v>
+      </c>
+      <c r="D91" t="s">
+        <v>28</v>
+      </c>
+      <c r="E91" t="s">
+        <v>177</v>
+      </c>
+      <c r="F91" t="s">
         <v>186</v>
-      </c>
-      <c r="C91" t="s">
-        <v>187</v>
-      </c>
-      <c r="D91" t="s">
-        <v>30</v>
-      </c>
-      <c r="E91" t="s">
-        <v>179</v>
-      </c>
-      <c r="F91" t="s">
-        <v>188</v>
       </c>
       <c r="G91" s="1">
         <v>70</v>
@@ -3202,68 +3194,68 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B92" t="s">
+        <v>187</v>
+      </c>
+      <c r="C92" t="s">
+        <v>188</v>
+      </c>
+      <c r="D92" t="s">
+        <v>28</v>
+      </c>
+      <c r="E92" t="s">
+        <v>29</v>
+      </c>
+      <c r="F92" t="s">
+        <v>186</v>
+      </c>
+      <c r="G92" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="C92" t="s">
-        <v>190</v>
-      </c>
-      <c r="D92" t="s">
-        <v>30</v>
-      </c>
-      <c r="E92" t="s">
-        <v>31</v>
-      </c>
-      <c r="F92" t="s">
-        <v>188</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B93" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C93" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D93" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E93" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F93" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
+        <v>166</v>
+      </c>
+      <c r="B94" t="s">
+        <v>192</v>
+      </c>
+      <c r="C94" t="s">
         <v>168</v>
       </c>
-      <c r="B94" t="s">
-        <v>194</v>
-      </c>
-      <c r="C94" t="s">
-        <v>170</v>
-      </c>
       <c r="D94" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E94" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F94" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G94" s="1">
         <v>70</v>
@@ -3271,68 +3263,68 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B95" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C95" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D95" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E95" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F95" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B96" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D96" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E96" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F96" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B97" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C97" t="s">
+        <v>176</v>
+      </c>
+      <c r="D97" t="s">
+        <v>66</v>
+      </c>
+      <c r="E97" t="s">
+        <v>177</v>
+      </c>
+      <c r="F97" t="s">
         <v>178</v>
-      </c>
-      <c r="D97" t="s">
-        <v>68</v>
-      </c>
-      <c r="E97" t="s">
-        <v>179</v>
-      </c>
-      <c r="F97" t="s">
-        <v>180</v>
       </c>
       <c r="G97" s="1">
         <v>70</v>
@@ -3340,68 +3332,68 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B98" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C98" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D98" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E98" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F98" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B99" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C99" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D99" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E99" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F99" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B100" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C100" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D100" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E100" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F100" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G100" s="1">
         <v>70</v>
@@ -3409,91 +3401,91 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B101" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C101" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D101" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E101" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F101" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B102" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C102" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D102" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E102" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F102" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B103" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C103" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D103" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E103" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F103" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
+        <v>166</v>
+      </c>
+      <c r="B104" t="s">
+        <v>204</v>
+      </c>
+      <c r="C104" t="s">
         <v>168</v>
       </c>
-      <c r="B104" t="s">
-        <v>206</v>
-      </c>
-      <c r="C104" t="s">
-        <v>170</v>
-      </c>
       <c r="D104" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E104" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F104" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G104" s="1">
         <v>70</v>
@@ -3501,22 +3493,22 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B105" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C105" t="s">
+        <v>176</v>
+      </c>
+      <c r="D105" t="s">
+        <v>128</v>
+      </c>
+      <c r="E105" t="s">
+        <v>177</v>
+      </c>
+      <c r="F105" t="s">
         <v>178</v>
-      </c>
-      <c r="D105" t="s">
-        <v>130</v>
-      </c>
-      <c r="E105" t="s">
-        <v>179</v>
-      </c>
-      <c r="F105" t="s">
-        <v>180</v>
       </c>
       <c r="G105" s="1">
         <v>70</v>
@@ -3524,45 +3516,45 @@
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B106" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C106" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D106" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E106" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F106" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B107" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C107" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D107" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E107" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F107" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G107" s="1">
         <v>70</v>
@@ -3570,68 +3562,68 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C108" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D108" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E108" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F108" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B109" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C109" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D109" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E109" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F109" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B110" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C110" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D110" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E110" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F110" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G110" s="1">
         <v>70</v>
@@ -3639,91 +3631,91 @@
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B111" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C111" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D111" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E111" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F111" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B112" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C112" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D112" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E112" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F112" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B113" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C113" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D113" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E113" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F113" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>166</v>
+      </c>
+      <c r="B114" t="s">
+        <v>216</v>
+      </c>
+      <c r="C114" t="s">
         <v>168</v>
       </c>
-      <c r="B114" t="s">
-        <v>218</v>
-      </c>
-      <c r="C114" t="s">
-        <v>170</v>
-      </c>
       <c r="D114" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E114" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F114" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G114" s="1">
         <v>70</v>
@@ -3731,91 +3723,91 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B115" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C115" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D115" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E115" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F115" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B116" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C116" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D116" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E116" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F116" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B117" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C117" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D117" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E117" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F117" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B118" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C118" t="s">
+        <v>176</v>
+      </c>
+      <c r="D118" t="s">
+        <v>210</v>
+      </c>
+      <c r="E118" t="s">
+        <v>177</v>
+      </c>
+      <c r="F118" t="s">
         <v>178</v>
-      </c>
-      <c r="D118" t="s">
-        <v>212</v>
-      </c>
-      <c r="E118" t="s">
-        <v>179</v>
-      </c>
-      <c r="F118" t="s">
-        <v>180</v>
       </c>
       <c r="G118" s="1">
         <v>70</v>
@@ -3823,91 +3815,91 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B119" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C119" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D119" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E119" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F119" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B120" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C120" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D120" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E120" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F120" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B121" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C121" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D121" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E121" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F121" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
+        <v>166</v>
+      </c>
+      <c r="B122" t="s">
+        <v>224</v>
+      </c>
+      <c r="C122" t="s">
         <v>168</v>
       </c>
-      <c r="B122" t="s">
-        <v>226</v>
-      </c>
-      <c r="C122" t="s">
-        <v>170</v>
-      </c>
       <c r="D122" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E122" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F122" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G122" s="1">
         <v>70</v>
@@ -3915,45 +3907,45 @@
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B123" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C123" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D123" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E123" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F123" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B124" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C124" t="s">
+        <v>176</v>
+      </c>
+      <c r="D124" t="s">
+        <v>226</v>
+      </c>
+      <c r="E124" t="s">
+        <v>177</v>
+      </c>
+      <c r="F124" t="s">
         <v>178</v>
-      </c>
-      <c r="D124" t="s">
-        <v>228</v>
-      </c>
-      <c r="E124" t="s">
-        <v>179</v>
-      </c>
-      <c r="F124" t="s">
-        <v>180</v>
       </c>
       <c r="G124" s="1">
         <v>70</v>
@@ -3961,45 +3953,45 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B125" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C125" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D125" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E125" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F125" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B126" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C126" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D126" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E126" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F126" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G126" s="1">
         <v>70</v>
@@ -4007,45 +3999,45 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B127" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C127" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D127" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E127" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F127" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>166</v>
+      </c>
+      <c r="B128" t="s">
+        <v>224</v>
+      </c>
+      <c r="C128" t="s">
         <v>168</v>
       </c>
-      <c r="B128" t="s">
-        <v>226</v>
-      </c>
-      <c r="C128" t="s">
-        <v>170</v>
-      </c>
       <c r="D128" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E128" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F128" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G128" s="1">
         <v>70</v>
@@ -4053,45 +4045,45 @@
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B129" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C129" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D129" t="s">
         <v>4</v>
       </c>
       <c r="E129" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F129" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B130" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C130" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D130" t="s">
         <v>4</v>
       </c>
       <c r="E130" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F130" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G130" s="1">
         <v>70</v>
@@ -4099,45 +4091,45 @@
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B131" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C131" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D131" t="s">
         <v>4</v>
       </c>
       <c r="E131" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F131" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B132" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C132" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D132" t="s">
         <v>4</v>
       </c>
       <c r="E132" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F132" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G132" s="1">
         <v>70</v>
@@ -4154,7 +4146,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -4229,14 +4221,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawn.hsieh\Desktop\隔熱紙下單小幫手\TMS148測試\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawn.hsieh\Desktop\隔熱紙下單小幫手\KIA\資料拆開版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7201704E-19D1-4454-ACB9-D82305C41F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7915D2EF-BCFD-4823-9AE4-899E2B883D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1605" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="隔熱紙" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="259">
   <si>
     <t>車型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -738,15 +738,9 @@
     <t>99PVYSMT4122JAYB</t>
   </si>
   <si>
-    <t xml:space="preserve"> 99PVYSM210A</t>
-  </si>
-  <si>
     <t>JA</t>
   </si>
   <si>
-    <t xml:space="preserve"> 99PVYSM212A</t>
-  </si>
-  <si>
     <t>99PVYSM010A</t>
   </si>
   <si>
@@ -763,6 +757,114 @@
   </si>
   <si>
     <t>99PVYSMYB2A</t>
+  </si>
+  <si>
+    <t>99PVYSM210A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVYSM212A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天窗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVYSMT4126JA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-天窗(T4-10,20,35,45,70)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JA PE2 SVP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Picanto Cappuccino</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVYSMT2126JA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-天窗(VEGA-05,15,30,40,50,70)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VEGA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVYSMT1126JA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-天窗(BELLA-05,15,30,40,70)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVYFSKB026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-天窗(KS20,KS40)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVYFSKKT026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-車身(KT系列,KT8,18.38,68)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-天窗(KT系列,KT8,18.38,68)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVYFSKF026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-天窗 S系列,S75,50,35,25,10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVYFSKTB126JAYB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-天窗(TB15,45,75)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVY3MMB126JAYB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVY3MMA126JAYB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>99PVY3MXC026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-天窗(極黑MB-05,20,30,38,45,60,75)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-天窗(極透MA-20,40.70,80,90)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隔熱紙-天窗(P18,35,40,70)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1088,15 +1190,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{278F8488-2E5D-430A-92BC-094A5D88171D}">
-  <dimension ref="A1:G132"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G142"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.8984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.69921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.8984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30.875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1725,22 +1827,22 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>244</v>
       </c>
       <c r="C28" t="s">
-        <v>39</v>
+        <v>245</v>
       </c>
       <c r="D28" t="s">
         <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="F28" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1748,22 +1850,22 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>247</v>
       </c>
       <c r="D29" t="s">
         <v>83</v>
       </c>
       <c r="E29" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F29" t="s">
         <v>40</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1771,22 +1873,22 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D30" t="s">
         <v>83</v>
       </c>
       <c r="E30" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1794,22 +1896,22 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>88</v>
+        <v>246</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
+        <v>248</v>
       </c>
       <c r="D31" t="s">
         <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>34</v>
+        <v>234</v>
       </c>
       <c r="F31" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1817,10 +1919,10 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="D32" t="s">
         <v>83</v>
@@ -1829,10 +1931,10 @@
         <v>29</v>
       </c>
       <c r="F32" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -1840,10 +1942,10 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D33" t="s">
         <v>83</v>
@@ -1852,10 +1954,10 @@
         <v>34</v>
       </c>
       <c r="F33" t="s">
-        <v>59</v>
-      </c>
-      <c r="G33" s="1">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -1863,22 +1965,22 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>249</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="D34" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -1886,22 +1988,22 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D35" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E35" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F35" t="s">
-        <v>67</v>
-      </c>
-      <c r="G35" s="1">
-        <v>78</v>
+        <v>59</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -1909,22 +2011,22 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F36" t="s">
-        <v>67</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>31</v>
+        <v>59</v>
+      </c>
+      <c r="G36" s="1">
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -1932,22 +2034,22 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>251</v>
       </c>
       <c r="C37" t="s">
-        <v>39</v>
+        <v>252</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E37" t="s">
-        <v>29</v>
+        <v>234</v>
       </c>
       <c r="F37" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -1955,22 +2057,22 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D38" t="s">
         <v>92</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -1978,22 +2080,22 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D39" t="s">
         <v>92</v>
       </c>
       <c r="E39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F39" t="s">
-        <v>40</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>41</v>
+        <v>67</v>
+      </c>
+      <c r="G39" s="1">
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -2001,22 +2103,22 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C40" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D40" t="s">
         <v>92</v>
       </c>
       <c r="E40" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F40" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -2024,22 +2126,22 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
         <v>92</v>
       </c>
       <c r="E41" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F41" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -2047,22 +2149,22 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="D42" t="s">
         <v>92</v>
       </c>
       <c r="E42" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="F42" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2070,22 +2172,22 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D43" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E43" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F43" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -2093,22 +2195,22 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D44" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E44" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F44" t="s">
-        <v>59</v>
-      </c>
-      <c r="G44" s="1">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2116,160 +2218,160 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C45" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="D45" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E45" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="D46" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="E46" t="s">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="F46" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>110</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
       <c r="D47" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E47" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F47" t="s">
-        <v>109</v>
-      </c>
-      <c r="G47" s="1">
-        <v>75</v>
+        <v>59</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="D48" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E48" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F48" t="s">
-        <v>115</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>116</v>
+        <v>59</v>
+      </c>
+      <c r="G48" s="1">
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C49" t="s">
-        <v>119</v>
+        <v>64</v>
       </c>
       <c r="D49" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E49" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="D50" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="E50" t="s">
         <v>29</v>
       </c>
       <c r="F50" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D51" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="E51" t="s">
         <v>34</v>
       </c>
       <c r="F51" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="G51" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -2277,22 +2379,22 @@
         <v>117</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>253</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>256</v>
       </c>
       <c r="D52" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E52" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F52" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2300,22 +2402,22 @@
         <v>117</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="C53" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D53" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E53" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F53" t="s">
-        <v>123</v>
-      </c>
-      <c r="G53" s="1">
-        <v>70</v>
+        <v>115</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -2323,22 +2425,22 @@
         <v>117</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C54" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="D54" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E54" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F54" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2346,22 +2448,22 @@
         <v>117</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>257</v>
       </c>
       <c r="D55" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E55" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G55" s="1">
-        <v>75</v>
+        <v>115</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2369,22 +2471,22 @@
         <v>117</v>
       </c>
       <c r="B56" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="E56" t="s">
         <v>29</v>
       </c>
       <c r="F56" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -2392,22 +2494,22 @@
         <v>117</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D57" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="E57" t="s">
         <v>34</v>
       </c>
       <c r="F57" t="s">
-        <v>115</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
+      </c>
+      <c r="G57" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -2415,16 +2517,16 @@
         <v>117</v>
       </c>
       <c r="B58" t="s">
-        <v>134</v>
+        <v>255</v>
       </c>
       <c r="C58" t="s">
-        <v>122</v>
+        <v>258</v>
       </c>
       <c r="D58" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="E58" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F58" t="s">
         <v>123</v>
@@ -2438,22 +2540,22 @@
         <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E59" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F59" t="s">
         <v>123</v>
       </c>
-      <c r="G59" s="1">
-        <v>70</v>
+      <c r="G59" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -2461,22 +2563,22 @@
         <v>117</v>
       </c>
       <c r="B60" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D60" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E60" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F60" t="s">
         <v>123</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>124</v>
+      <c r="G60" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -2484,13 +2586,13 @@
         <v>117</v>
       </c>
       <c r="B61" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C61" t="s">
         <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E61" t="s">
         <v>29</v>
@@ -2507,13 +2609,13 @@
         <v>117</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C62" t="s">
         <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E62" t="s">
         <v>34</v>
@@ -2530,22 +2632,22 @@
         <v>117</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="C63" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="D63" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E63" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F63" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -2553,22 +2655,22 @@
         <v>117</v>
       </c>
       <c r="B64" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C64" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D64" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E64" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F64" t="s">
         <v>115</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -2576,22 +2678,22 @@
         <v>117</v>
       </c>
       <c r="B65" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C65" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
         <v>135</v>
       </c>
       <c r="E65" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F65" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -2599,22 +2701,22 @@
         <v>117</v>
       </c>
       <c r="B66" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="C66" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D66" t="s">
         <v>135</v>
       </c>
       <c r="E66" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F66" t="s">
-        <v>115</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="G66" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -2622,16 +2724,16 @@
         <v>117</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C67" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D67" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E67" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F67" t="s">
         <v>123</v>
@@ -2645,22 +2747,22 @@
         <v>117</v>
       </c>
       <c r="B68" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C68" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D68" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E68" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F68" t="s">
-        <v>123</v>
-      </c>
-      <c r="G68" s="1">
-        <v>70</v>
+        <v>109</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -2668,22 +2770,22 @@
         <v>117</v>
       </c>
       <c r="B69" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C69" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E69" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F69" t="s">
-        <v>123</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
+      </c>
+      <c r="G69" s="1">
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -2691,16 +2793,16 @@
         <v>117</v>
       </c>
       <c r="B70" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C70" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="D70" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E70" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F70" t="s">
         <v>109</v>
@@ -2714,22 +2816,22 @@
         <v>117</v>
       </c>
       <c r="B71" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D71" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E71" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F71" t="s">
-        <v>109</v>
-      </c>
-      <c r="G71" s="1">
-        <v>75</v>
+        <v>115</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -2737,22 +2839,22 @@
         <v>117</v>
       </c>
       <c r="B72" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C72" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="D72" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E72" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F72" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -2760,16 +2862,16 @@
         <v>117</v>
       </c>
       <c r="B73" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C73" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="E73" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F73" t="s">
         <v>115</v>
@@ -2783,22 +2885,22 @@
         <v>117</v>
       </c>
       <c r="B74" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C74" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D74" t="s">
         <v>148</v>
       </c>
       <c r="E74" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F74" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -2806,22 +2908,22 @@
         <v>117</v>
       </c>
       <c r="B75" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C75" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D75" t="s">
         <v>148</v>
       </c>
       <c r="E75" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F75" t="s">
-        <v>115</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="G75" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -2829,16 +2931,16 @@
         <v>117</v>
       </c>
       <c r="B76" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C76" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D76" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="E76" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F76" t="s">
         <v>123</v>
@@ -2852,22 +2954,22 @@
         <v>117</v>
       </c>
       <c r="B77" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C77" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D77" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="E77" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F77" t="s">
-        <v>123</v>
-      </c>
-      <c r="G77" s="1">
-        <v>70</v>
+        <v>109</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -2875,22 +2977,22 @@
         <v>117</v>
       </c>
       <c r="B78" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C78" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="D78" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="E78" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F78" t="s">
-        <v>123</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>124</v>
+        <v>109</v>
+      </c>
+      <c r="G78" s="1">
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -2898,16 +3000,16 @@
         <v>117</v>
       </c>
       <c r="B79" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C79" t="s">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="D79" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="E79" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F79" t="s">
         <v>109</v>
@@ -2921,22 +3023,22 @@
         <v>117</v>
       </c>
       <c r="B80" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D80" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="E80" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F80" t="s">
-        <v>109</v>
-      </c>
-      <c r="G80" s="1">
-        <v>75</v>
+        <v>115</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -2944,22 +3046,22 @@
         <v>117</v>
       </c>
       <c r="B81" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C81" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="D81" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="E81" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F81" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -2967,16 +3069,16 @@
         <v>117</v>
       </c>
       <c r="B82" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C82" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="D82" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="E82" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F82" t="s">
         <v>115</v>
@@ -2990,22 +3092,22 @@
         <v>117</v>
       </c>
       <c r="B83" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C83" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D83" t="s">
         <v>66</v>
       </c>
       <c r="E83" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F83" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -3013,183 +3115,183 @@
         <v>117</v>
       </c>
       <c r="B84" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C84" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D84" t="s">
         <v>66</v>
       </c>
       <c r="E84" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F84" t="s">
-        <v>115</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="G84" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B85" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C85" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="D85" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="E85" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F85" t="s">
-        <v>169</v>
-      </c>
-      <c r="G85" s="1">
-        <v>70</v>
+        <v>123</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B86" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C86" t="s">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="E86" t="s">
         <v>29</v>
       </c>
       <c r="F86" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>172</v>
+        <v>110</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B87" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C87" t="s">
-        <v>174</v>
+        <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="E87" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F87" t="s">
-        <v>169</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>172</v>
+        <v>109</v>
+      </c>
+      <c r="G87" s="1">
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="C88" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="D88" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="E88" t="s">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="F88" t="s">
-        <v>178</v>
-      </c>
-      <c r="G88" s="1">
-        <v>70</v>
+        <v>109</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B89" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="C89" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="E89" t="s">
         <v>29</v>
       </c>
       <c r="F89" t="s">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>181</v>
+        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B90" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="C90" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="D90" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="E90" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F90" t="s">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>181</v>
+        <v>120</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="C91" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="D91" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="E91" t="s">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="F91" t="s">
-        <v>186</v>
-      </c>
-      <c r="G91" s="1">
-        <v>70</v>
+        <v>115</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -3197,22 +3299,22 @@
         <v>166</v>
       </c>
       <c r="B92" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C92" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="D92" t="s">
         <v>28</v>
       </c>
       <c r="E92" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F92" t="s">
-        <v>186</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>189</v>
+        <v>169</v>
+      </c>
+      <c r="G92" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -3220,22 +3322,22 @@
         <v>166</v>
       </c>
       <c r="B93" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="C93" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="D93" t="s">
         <v>28</v>
       </c>
       <c r="E93" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F93" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -3243,22 +3345,22 @@
         <v>166</v>
       </c>
       <c r="B94" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="C94" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D94" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="E94" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F94" t="s">
         <v>169</v>
       </c>
-      <c r="G94" s="1">
-        <v>70</v>
+      <c r="G94" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -3266,22 +3368,22 @@
         <v>166</v>
       </c>
       <c r="B95" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C95" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D95" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="E95" t="s">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="F95" t="s">
-        <v>169</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
+      </c>
+      <c r="G95" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -3289,22 +3391,22 @@
         <v>166</v>
       </c>
       <c r="B96" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C96" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D96" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="E96" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F96" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -3312,22 +3414,22 @@
         <v>166</v>
       </c>
       <c r="B97" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="C97" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D97" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="E97" t="s">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="F97" t="s">
         <v>178</v>
       </c>
-      <c r="G97" s="1">
-        <v>70</v>
+      <c r="G97" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -3335,22 +3437,22 @@
         <v>166</v>
       </c>
       <c r="B98" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="C98" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D98" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="E98" t="s">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="F98" t="s">
-        <v>178</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
+      </c>
+      <c r="G98" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -3358,22 +3460,22 @@
         <v>166</v>
       </c>
       <c r="B99" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C99" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D99" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="E99" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F99" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -3381,22 +3483,22 @@
         <v>166</v>
       </c>
       <c r="B100" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C100" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D100" t="s">
-        <v>199</v>
+        <v>28</v>
       </c>
       <c r="E100" t="s">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="F100" t="s">
         <v>186</v>
       </c>
-      <c r="G100" s="1">
-        <v>70</v>
+      <c r="G100" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -3404,22 +3506,22 @@
         <v>166</v>
       </c>
       <c r="B101" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C101" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="D101" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="E101" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F101" t="s">
-        <v>186</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>189</v>
+        <v>169</v>
+      </c>
+      <c r="G101" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
@@ -3427,22 +3529,22 @@
         <v>166</v>
       </c>
       <c r="B102" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C102" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="D102" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="E102" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F102" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -3450,16 +3552,16 @@
         <v>166</v>
       </c>
       <c r="B103" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C103" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D103" t="s">
-        <v>203</v>
+        <v>66</v>
       </c>
       <c r="E103" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F103" t="s">
         <v>169</v>
@@ -3473,19 +3575,19 @@
         <v>166</v>
       </c>
       <c r="B104" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C104" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D104" t="s">
-        <v>203</v>
+        <v>66</v>
       </c>
       <c r="E104" t="s">
-        <v>34</v>
+        <v>177</v>
       </c>
       <c r="F104" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G104" s="1">
         <v>70</v>
@@ -3496,22 +3598,22 @@
         <v>166</v>
       </c>
       <c r="B105" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C105" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D105" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="E105" t="s">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="F105" t="s">
         <v>178</v>
       </c>
-      <c r="G105" s="1">
-        <v>70</v>
+      <c r="G105" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
@@ -3519,16 +3621,16 @@
         <v>166</v>
       </c>
       <c r="B106" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C106" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D106" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="E106" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F106" t="s">
         <v>178</v>
@@ -3542,13 +3644,13 @@
         <v>166</v>
       </c>
       <c r="B107" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C107" t="s">
         <v>185</v>
       </c>
       <c r="D107" t="s">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="E107" t="s">
         <v>177</v>
@@ -3565,13 +3667,13 @@
         <v>166</v>
       </c>
       <c r="B108" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C108" t="s">
         <v>188</v>
       </c>
       <c r="D108" t="s">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="E108" t="s">
         <v>29</v>
@@ -3588,16 +3690,16 @@
         <v>166</v>
       </c>
       <c r="B109" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C109" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D109" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E109" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F109" t="s">
         <v>186</v>
@@ -3611,22 +3713,22 @@
         <v>166</v>
       </c>
       <c r="B110" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C110" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D110" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E110" t="s">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="F110" t="s">
-        <v>186</v>
-      </c>
-      <c r="G110" s="1">
-        <v>70</v>
+        <v>169</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
@@ -3634,22 +3736,22 @@
         <v>166</v>
       </c>
       <c r="B111" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C111" t="s">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="D111" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="E111" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F111" t="s">
-        <v>186</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>189</v>
+        <v>169</v>
+      </c>
+      <c r="G111" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
@@ -3657,22 +3759,22 @@
         <v>166</v>
       </c>
       <c r="B112" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="C112" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="D112" t="s">
-        <v>214</v>
+        <v>128</v>
       </c>
       <c r="E112" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="F112" t="s">
-        <v>186</v>
-      </c>
-      <c r="G112" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
+      </c>
+      <c r="G112" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
@@ -3680,22 +3782,22 @@
         <v>166</v>
       </c>
       <c r="B113" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="C113" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="D113" t="s">
-        <v>210</v>
+        <v>128</v>
       </c>
       <c r="E113" t="s">
         <v>29</v>
       </c>
       <c r="F113" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
@@ -3703,19 +3805,19 @@
         <v>166</v>
       </c>
       <c r="B114" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="C114" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="D114" t="s">
-        <v>210</v>
+        <v>128</v>
       </c>
       <c r="E114" t="s">
-        <v>34</v>
+        <v>177</v>
       </c>
       <c r="F114" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="G114" s="1">
         <v>70</v>
@@ -3726,22 +3828,22 @@
         <v>166</v>
       </c>
       <c r="B115" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C115" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D115" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E115" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F115" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
@@ -3749,22 +3851,22 @@
         <v>166</v>
       </c>
       <c r="B116" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="C116" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D116" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E116" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F116" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
@@ -3772,22 +3874,22 @@
         <v>166</v>
       </c>
       <c r="B117" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="C117" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D117" t="s">
         <v>210</v>
       </c>
       <c r="E117" t="s">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="F117" t="s">
-        <v>178</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
+      </c>
+      <c r="G117" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
@@ -3795,22 +3897,22 @@
         <v>166</v>
       </c>
       <c r="B118" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="C118" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="D118" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="E118" t="s">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="F118" t="s">
-        <v>178</v>
-      </c>
-      <c r="G118" s="1">
-        <v>70</v>
+        <v>186</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
@@ -3818,22 +3920,22 @@
         <v>166</v>
       </c>
       <c r="B119" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="C119" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D119" t="s">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="E119" t="s">
         <v>37</v>
       </c>
       <c r="F119" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
@@ -3841,22 +3943,22 @@
         <v>166</v>
       </c>
       <c r="B120" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C120" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D120" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E120" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F120" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
@@ -3864,22 +3966,22 @@
         <v>166</v>
       </c>
       <c r="B121" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C121" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D121" t="s">
-        <v>83</v>
+        <v>210</v>
       </c>
       <c r="E121" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F121" t="s">
         <v>169</v>
       </c>
-      <c r="G121" s="1" t="s">
-        <v>172</v>
+      <c r="G121" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
@@ -3887,22 +3989,22 @@
         <v>166</v>
       </c>
       <c r="B122" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C122" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D122" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="E122" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F122" t="s">
         <v>169</v>
       </c>
-      <c r="G122" s="1">
-        <v>70</v>
+      <c r="G122" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
@@ -3910,22 +4012,22 @@
         <v>166</v>
       </c>
       <c r="B123" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="C123" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D123" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="E123" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F123" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
@@ -3933,22 +4035,22 @@
         <v>166</v>
       </c>
       <c r="B124" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="C124" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D124" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E124" t="s">
-        <v>177</v>
+        <v>29</v>
       </c>
       <c r="F124" t="s">
         <v>178</v>
       </c>
-      <c r="G124" s="1">
-        <v>70</v>
+      <c r="G124" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
@@ -3956,22 +4058,22 @@
         <v>166</v>
       </c>
       <c r="B125" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="C125" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D125" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E125" t="s">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="F125" t="s">
-        <v>186</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>189</v>
+        <v>178</v>
+      </c>
+      <c r="G125" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
@@ -3979,22 +4081,22 @@
         <v>166</v>
       </c>
       <c r="B126" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C126" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D126" t="s">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="E126" t="s">
-        <v>177</v>
+        <v>37</v>
       </c>
       <c r="F126" t="s">
-        <v>186</v>
-      </c>
-      <c r="G126" s="1">
-        <v>70</v>
+        <v>178</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
@@ -4002,22 +4104,22 @@
         <v>166</v>
       </c>
       <c r="B127" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C127" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D127" t="s">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="E127" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F127" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
@@ -4025,22 +4127,22 @@
         <v>166</v>
       </c>
       <c r="B128" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C128" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D128" t="s">
         <v>83</v>
       </c>
       <c r="E128" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F128" t="s">
         <v>169</v>
       </c>
-      <c r="G128" s="1">
-        <v>70</v>
+      <c r="G128" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
@@ -4048,22 +4150,22 @@
         <v>166</v>
       </c>
       <c r="B129" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C129" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D129" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="E129" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F129" t="s">
-        <v>178</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>181</v>
+        <v>169</v>
+      </c>
+      <c r="G129" s="1">
+        <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
@@ -4071,22 +4173,22 @@
         <v>166</v>
       </c>
       <c r="B130" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C130" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="D130" t="s">
-        <v>4</v>
+        <v>237</v>
       </c>
       <c r="E130" t="s">
-        <v>177</v>
+        <v>234</v>
       </c>
       <c r="F130" t="s">
-        <v>178</v>
-      </c>
-      <c r="G130" s="1">
-        <v>70</v>
+        <v>169</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
@@ -4097,19 +4199,19 @@
         <v>232</v>
       </c>
       <c r="C131" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="D131" t="s">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="E131" t="s">
         <v>29</v>
       </c>
       <c r="F131" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
@@ -4120,18 +4222,248 @@
         <v>233</v>
       </c>
       <c r="C132" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="D132" t="s">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="E132" t="s">
         <v>177</v>
       </c>
       <c r="F132" t="s">
+        <v>178</v>
+      </c>
+      <c r="G132" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>166</v>
+      </c>
+      <c r="B133" t="s">
+        <v>239</v>
+      </c>
+      <c r="C133" t="s">
+        <v>240</v>
+      </c>
+      <c r="D133" t="s">
+        <v>237</v>
+      </c>
+      <c r="E133" t="s">
+        <v>234</v>
+      </c>
+      <c r="F133" t="s">
+        <v>241</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>166</v>
+      </c>
+      <c r="B134" t="s">
+        <v>226</v>
+      </c>
+      <c r="C134" t="s">
+        <v>188</v>
+      </c>
+      <c r="D134" t="s">
+        <v>225</v>
+      </c>
+      <c r="E134" t="s">
+        <v>29</v>
+      </c>
+      <c r="F134" t="s">
         <v>186</v>
       </c>
-      <c r="G132" s="1">
+      <c r="G134" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>166</v>
+      </c>
+      <c r="B135" t="s">
+        <v>227</v>
+      </c>
+      <c r="C135" t="s">
+        <v>185</v>
+      </c>
+      <c r="D135" t="s">
+        <v>225</v>
+      </c>
+      <c r="E135" t="s">
+        <v>177</v>
+      </c>
+      <c r="F135" t="s">
+        <v>186</v>
+      </c>
+      <c r="G135" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>166</v>
+      </c>
+      <c r="B136" t="s">
+        <v>242</v>
+      </c>
+      <c r="C136" t="s">
+        <v>243</v>
+      </c>
+      <c r="D136" t="s">
+        <v>225</v>
+      </c>
+      <c r="E136" t="s">
+        <v>234</v>
+      </c>
+      <c r="F136" t="s">
+        <v>186</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>166</v>
+      </c>
+      <c r="B137" t="s">
+        <v>223</v>
+      </c>
+      <c r="C137" t="s">
+        <v>171</v>
+      </c>
+      <c r="D137" t="s">
+        <v>83</v>
+      </c>
+      <c r="E137" t="s">
+        <v>29</v>
+      </c>
+      <c r="F137" t="s">
+        <v>169</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>166</v>
+      </c>
+      <c r="B138" t="s">
+        <v>224</v>
+      </c>
+      <c r="C138" t="s">
+        <v>168</v>
+      </c>
+      <c r="D138" t="s">
+        <v>83</v>
+      </c>
+      <c r="E138" t="s">
+        <v>34</v>
+      </c>
+      <c r="F138" t="s">
+        <v>169</v>
+      </c>
+      <c r="G138" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>166</v>
+      </c>
+      <c r="B139" t="s">
+        <v>228</v>
+      </c>
+      <c r="C139" t="s">
+        <v>180</v>
+      </c>
+      <c r="D139" t="s">
+        <v>4</v>
+      </c>
+      <c r="E139" t="s">
+        <v>29</v>
+      </c>
+      <c r="F139" t="s">
+        <v>178</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>166</v>
+      </c>
+      <c r="B140" t="s">
+        <v>229</v>
+      </c>
+      <c r="C140" t="s">
+        <v>176</v>
+      </c>
+      <c r="D140" t="s">
+        <v>4</v>
+      </c>
+      <c r="E140" t="s">
+        <v>177</v>
+      </c>
+      <c r="F140" t="s">
+        <v>178</v>
+      </c>
+      <c r="G140" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>166</v>
+      </c>
+      <c r="B141" t="s">
+        <v>230</v>
+      </c>
+      <c r="C141" t="s">
+        <v>188</v>
+      </c>
+      <c r="D141" t="s">
+        <v>4</v>
+      </c>
+      <c r="E141" t="s">
+        <v>29</v>
+      </c>
+      <c r="F141" t="s">
+        <v>186</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>166</v>
+      </c>
+      <c r="B142" t="s">
+        <v>231</v>
+      </c>
+      <c r="C142" t="s">
+        <v>185</v>
+      </c>
+      <c r="D142" t="s">
+        <v>4</v>
+      </c>
+      <c r="E142" t="s">
+        <v>177</v>
+      </c>
+      <c r="F142" t="s">
+        <v>186</v>
+      </c>
+      <c r="G142" s="1">
         <v>70</v>
       </c>
     </row>
@@ -4139,15 +4471,15 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="G6:G27 G29:G133" numberStoredAsText="1"/>
+    <ignoredError sqref="G6:G27 G137:G143 G59:G129 G131:G132 G134:G135 G30 G32:G33 G35:G36 G38:G51 G53:G54 G56:G57" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -4219,6 +4551,14 @@
       </c>
       <c r="B9" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawn.hsieh\Desktop\隔熱紙下單小幫手\KIA\資料拆開版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7915D2EF-BCFD-4823-9AE4-899E2B883D60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463BFA29-A285-408F-B7FC-450974CB3DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="隔熱紙" sheetId="2" r:id="rId1"/>
     <sheet name="車型" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">隔熱紙!$A$1:$G$142</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="256">
   <si>
     <t>車型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -385,9 +388,6 @@
     <t>隔熱紙-車身(極黑MB-05,20,30,38,45,60,75)</t>
   </si>
   <si>
-    <t>JA PE, YB PE</t>
-  </si>
-  <si>
     <t>極黑MB</t>
   </si>
   <si>
@@ -776,14 +776,6 @@
   </si>
   <si>
     <t>隔熱紙-天窗(T4-10,20,35,45,70)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>JA PE2 SVP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Picanto Cappuccino</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1827,16 +1819,16 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C28" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D28" t="s">
         <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F28" t="s">
         <v>30</v>
@@ -1853,7 +1845,7 @@
         <v>85</v>
       </c>
       <c r="C29" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D29" t="s">
         <v>83</v>
@@ -1896,16 +1888,16 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C31" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D31" t="s">
         <v>83</v>
       </c>
       <c r="E31" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F31" t="s">
         <v>40</v>
@@ -1965,16 +1957,16 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C34" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D34" t="s">
         <v>83</v>
       </c>
       <c r="E34" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F34" t="s">
         <v>74</v>
@@ -2034,16 +2026,16 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C37" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D37" t="s">
         <v>83</v>
       </c>
       <c r="E37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F37" t="s">
         <v>59</v>
@@ -2339,16 +2331,16 @@
         <v>107</v>
       </c>
       <c r="D50" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50" t="s">
         <v>108</v>
       </c>
-      <c r="E50" t="s">
-        <v>29</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="G50" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -2356,19 +2348,19 @@
         <v>105</v>
       </c>
       <c r="B51" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" t="s">
         <v>111</v>
       </c>
-      <c r="C51" t="s">
-        <v>112</v>
-      </c>
       <c r="D51" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E51" t="s">
         <v>34</v>
       </c>
       <c r="F51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G51" s="1">
         <v>75</v>
@@ -2376,105 +2368,105 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
+        <v>250</v>
+      </c>
+      <c r="C52" t="s">
         <v>253</v>
       </c>
-      <c r="C52" t="s">
-        <v>256</v>
-      </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E52" t="s">
         <v>37</v>
       </c>
       <c r="F52" t="s">
+        <v>108</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B53" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" t="s">
         <v>113</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
+        <v>83</v>
+      </c>
+      <c r="E53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53" t="s">
         <v>114</v>
       </c>
-      <c r="D53" t="s">
-        <v>108</v>
-      </c>
-      <c r="E53" t="s">
-        <v>29</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="G53" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>116</v>
+      </c>
+      <c r="B54" t="s">
         <v>117</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>118</v>
       </c>
-      <c r="C54" t="s">
-        <v>119</v>
-      </c>
       <c r="D54" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E54" t="s">
         <v>34</v>
       </c>
       <c r="F54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B55" t="s">
+        <v>251</v>
+      </c>
+      <c r="C55" t="s">
         <v>254</v>
       </c>
-      <c r="C55" t="s">
-        <v>257</v>
-      </c>
       <c r="D55" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="E55" t="s">
         <v>37</v>
       </c>
       <c r="F55" t="s">
+        <v>114</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C56" t="s">
         <v>121</v>
-      </c>
-      <c r="C56" t="s">
-        <v>122</v>
       </c>
       <c r="D56" t="s">
         <v>83</v>
@@ -2483,21 +2475,21 @@
         <v>29</v>
       </c>
       <c r="F56" t="s">
+        <v>122</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B57" t="s">
+        <v>124</v>
+      </c>
+      <c r="C57" t="s">
         <v>125</v>
-      </c>
-      <c r="C57" t="s">
-        <v>126</v>
       </c>
       <c r="D57" t="s">
         <v>83</v>
@@ -2506,7 +2498,7 @@
         <v>34</v>
       </c>
       <c r="F57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G57" s="1">
         <v>70</v>
@@ -2514,13 +2506,13 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B58" t="s">
+        <v>252</v>
+      </c>
+      <c r="C58" t="s">
         <v>255</v>
-      </c>
-      <c r="C58" t="s">
-        <v>258</v>
       </c>
       <c r="D58" t="s">
         <v>83</v>
@@ -2529,53 +2521,53 @@
         <v>37</v>
       </c>
       <c r="F58" t="s">
+        <v>122</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" t="s">
+        <v>121</v>
+      </c>
+      <c r="D59" t="s">
         <v>127</v>
       </c>
-      <c r="C59" t="s">
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59" t="s">
         <v>122</v>
       </c>
-      <c r="D59" t="s">
-        <v>128</v>
-      </c>
-      <c r="E59" t="s">
-        <v>29</v>
-      </c>
-      <c r="F59" t="s">
+      <c r="G59" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C60" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D60" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E60" t="s">
         <v>34</v>
       </c>
       <c r="F60" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G60" s="1">
         <v>70</v>
@@ -2583,45 +2575,45 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B61" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C61" t="s">
         <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E61" t="s">
         <v>29</v>
       </c>
       <c r="F61" t="s">
+        <v>108</v>
+      </c>
+      <c r="G61" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B62" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E62" t="s">
         <v>34</v>
       </c>
       <c r="F62" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G62" s="1">
         <v>75</v>
@@ -2629,91 +2621,91 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s">
+        <v>113</v>
+      </c>
+      <c r="D63" t="s">
+        <v>127</v>
+      </c>
+      <c r="E63" t="s">
+        <v>29</v>
+      </c>
+      <c r="F63" t="s">
         <v>114</v>
       </c>
-      <c r="D63" t="s">
-        <v>128</v>
-      </c>
-      <c r="E63" t="s">
-        <v>29</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="G63" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B64" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D64" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E64" t="s">
         <v>34</v>
       </c>
       <c r="F64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B65" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" t="s">
+        <v>121</v>
+      </c>
+      <c r="D65" t="s">
         <v>134</v>
       </c>
-      <c r="C65" t="s">
+      <c r="E65" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65" t="s">
         <v>122</v>
       </c>
-      <c r="D65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E65" t="s">
-        <v>29</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="G65" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C66" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E66" t="s">
         <v>34</v>
       </c>
       <c r="F66" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G66" s="1">
         <v>70</v>
@@ -2721,68 +2713,68 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B67" t="s">
+        <v>136</v>
+      </c>
+      <c r="C67" t="s">
         <v>137</v>
       </c>
-      <c r="C67" t="s">
-        <v>138</v>
-      </c>
       <c r="D67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E67" t="s">
         <v>37</v>
       </c>
       <c r="F67" t="s">
+        <v>122</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C68" t="s">
         <v>107</v>
       </c>
       <c r="D68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E68" t="s">
         <v>29</v>
       </c>
       <c r="F68" t="s">
+        <v>108</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B69" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D69" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E69" t="s">
         <v>34</v>
       </c>
       <c r="F69" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G69" s="1">
         <v>75</v>
@@ -2790,137 +2782,137 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B70" t="s">
+        <v>140</v>
+      </c>
+      <c r="C70" t="s">
         <v>141</v>
       </c>
-      <c r="C70" t="s">
-        <v>142</v>
-      </c>
       <c r="D70" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E70" t="s">
         <v>37</v>
       </c>
       <c r="F70" t="s">
+        <v>108</v>
+      </c>
+      <c r="G70" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B71" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C71" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" t="s">
+        <v>134</v>
+      </c>
+      <c r="E71" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71" t="s">
         <v>114</v>
       </c>
-      <c r="D71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E71" t="s">
-        <v>29</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="G71" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B72" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C72" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D72" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E72" t="s">
         <v>34</v>
       </c>
       <c r="F72" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B73" t="s">
+        <v>144</v>
+      </c>
+      <c r="C73" t="s">
         <v>145</v>
       </c>
-      <c r="C73" t="s">
-        <v>146</v>
-      </c>
       <c r="D73" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E73" t="s">
         <v>37</v>
       </c>
       <c r="F73" t="s">
+        <v>114</v>
+      </c>
+      <c r="G73" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B74" t="s">
+        <v>146</v>
+      </c>
+      <c r="C74" t="s">
+        <v>121</v>
+      </c>
+      <c r="D74" t="s">
         <v>147</v>
       </c>
-      <c r="C74" t="s">
+      <c r="E74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74" t="s">
         <v>122</v>
       </c>
-      <c r="D74" t="s">
-        <v>148</v>
-      </c>
-      <c r="E74" t="s">
-        <v>29</v>
-      </c>
-      <c r="F74" t="s">
+      <c r="G74" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B75" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C75" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D75" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E75" t="s">
         <v>34</v>
       </c>
       <c r="F75" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G75" s="1">
         <v>70</v>
@@ -2928,68 +2920,68 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B76" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C76" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D76" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E76" t="s">
         <v>37</v>
       </c>
       <c r="F76" t="s">
+        <v>122</v>
+      </c>
+      <c r="G76" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B77" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C77" t="s">
         <v>107</v>
       </c>
       <c r="D77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E77" t="s">
         <v>29</v>
       </c>
       <c r="F77" t="s">
+        <v>108</v>
+      </c>
+      <c r="G77" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B78" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D78" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E78" t="s">
         <v>34</v>
       </c>
       <c r="F78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G78" s="1">
         <v>75</v>
@@ -2997,105 +2989,105 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B79" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D79" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E79" t="s">
         <v>37</v>
       </c>
       <c r="F79" t="s">
+        <v>108</v>
+      </c>
+      <c r="G79" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B80" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C80" t="s">
+        <v>113</v>
+      </c>
+      <c r="D80" t="s">
+        <v>147</v>
+      </c>
+      <c r="E80" t="s">
+        <v>29</v>
+      </c>
+      <c r="F80" t="s">
         <v>114</v>
       </c>
-      <c r="D80" t="s">
-        <v>148</v>
-      </c>
-      <c r="E80" t="s">
-        <v>29</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="G80" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B81" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C81" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D81" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E81" t="s">
         <v>34</v>
       </c>
       <c r="F81" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C82" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D82" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E82" t="s">
         <v>37</v>
       </c>
       <c r="F82" t="s">
+        <v>114</v>
+      </c>
+      <c r="G82" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B83" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C83" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D83" t="s">
         <v>66</v>
@@ -3104,21 +3096,21 @@
         <v>29</v>
       </c>
       <c r="F83" t="s">
+        <v>122</v>
+      </c>
+      <c r="G83" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B84" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C84" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D84" t="s">
         <v>66</v>
@@ -3127,7 +3119,7 @@
         <v>34</v>
       </c>
       <c r="F84" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G84" s="1">
         <v>70</v>
@@ -3135,13 +3127,13 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B85" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C85" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D85" t="s">
         <v>66</v>
@@ -3150,18 +3142,18 @@
         <v>37</v>
       </c>
       <c r="F85" t="s">
+        <v>122</v>
+      </c>
+      <c r="G85" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B86" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C86" t="s">
         <v>107</v>
@@ -3173,21 +3165,21 @@
         <v>29</v>
       </c>
       <c r="F86" t="s">
+        <v>108</v>
+      </c>
+      <c r="G86" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B87" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D87" t="s">
         <v>66</v>
@@ -3196,7 +3188,7 @@
         <v>34</v>
       </c>
       <c r="F87" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G87" s="1">
         <v>75</v>
@@ -3204,13 +3196,13 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B88" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C88" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D88" t="s">
         <v>66</v>
@@ -3219,21 +3211,21 @@
         <v>37</v>
       </c>
       <c r="F88" t="s">
+        <v>108</v>
+      </c>
+      <c r="G88" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B89" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C89" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D89" t="s">
         <v>66</v>
@@ -3242,21 +3234,21 @@
         <v>29</v>
       </c>
       <c r="F89" t="s">
+        <v>114</v>
+      </c>
+      <c r="G89" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B90" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C90" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D90" t="s">
         <v>66</v>
@@ -3265,21 +3257,21 @@
         <v>34</v>
       </c>
       <c r="F90" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B91" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C91" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D91" t="s">
         <v>66</v>
@@ -3288,21 +3280,21 @@
         <v>37</v>
       </c>
       <c r="F91" t="s">
+        <v>114</v>
+      </c>
+      <c r="G91" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>165</v>
+      </c>
+      <c r="B92" t="s">
         <v>166</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>167</v>
-      </c>
-      <c r="C92" t="s">
-        <v>168</v>
       </c>
       <c r="D92" t="s">
         <v>28</v>
@@ -3311,7 +3303,7 @@
         <v>34</v>
       </c>
       <c r="F92" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G92" s="1">
         <v>70</v>
@@ -3319,13 +3311,13 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B93" t="s">
+        <v>169</v>
+      </c>
+      <c r="C93" t="s">
         <v>170</v>
-      </c>
-      <c r="C93" t="s">
-        <v>171</v>
       </c>
       <c r="D93" t="s">
         <v>28</v>
@@ -3334,21 +3326,21 @@
         <v>29</v>
       </c>
       <c r="F93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B94" t="s">
+        <v>172</v>
+      </c>
+      <c r="C94" t="s">
         <v>173</v>
-      </c>
-      <c r="C94" t="s">
-        <v>174</v>
       </c>
       <c r="D94" t="s">
         <v>28</v>
@@ -3357,30 +3349,30 @@
         <v>37</v>
       </c>
       <c r="F94" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B95" t="s">
+        <v>174</v>
+      </c>
+      <c r="C95" t="s">
         <v>175</v>
-      </c>
-      <c r="C95" t="s">
-        <v>176</v>
       </c>
       <c r="D95" t="s">
         <v>28</v>
       </c>
       <c r="E95" t="s">
+        <v>176</v>
+      </c>
+      <c r="F95" t="s">
         <v>177</v>
-      </c>
-      <c r="F95" t="s">
-        <v>178</v>
       </c>
       <c r="G95" s="1">
         <v>70</v>
@@ -3388,13 +3380,13 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B96" t="s">
+        <v>178</v>
+      </c>
+      <c r="C96" t="s">
         <v>179</v>
-      </c>
-      <c r="C96" t="s">
-        <v>180</v>
       </c>
       <c r="D96" t="s">
         <v>28</v>
@@ -3403,21 +3395,21 @@
         <v>29</v>
       </c>
       <c r="F96" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B97" t="s">
+        <v>181</v>
+      </c>
+      <c r="C97" t="s">
         <v>182</v>
-      </c>
-      <c r="C97" t="s">
-        <v>183</v>
       </c>
       <c r="D97" t="s">
         <v>28</v>
@@ -3426,30 +3418,30 @@
         <v>37</v>
       </c>
       <c r="F97" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B98" t="s">
+        <v>183</v>
+      </c>
+      <c r="C98" t="s">
         <v>184</v>
-      </c>
-      <c r="C98" t="s">
-        <v>185</v>
       </c>
       <c r="D98" t="s">
         <v>28</v>
       </c>
       <c r="E98" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F98" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G98" s="1">
         <v>70</v>
@@ -3457,13 +3449,13 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B99" t="s">
+        <v>186</v>
+      </c>
+      <c r="C99" t="s">
         <v>187</v>
-      </c>
-      <c r="C99" t="s">
-        <v>188</v>
       </c>
       <c r="D99" t="s">
         <v>28</v>
@@ -3472,21 +3464,21 @@
         <v>29</v>
       </c>
       <c r="F99" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B100" t="s">
+        <v>189</v>
+      </c>
+      <c r="C100" t="s">
         <v>190</v>
-      </c>
-      <c r="C100" t="s">
-        <v>191</v>
       </c>
       <c r="D100" t="s">
         <v>28</v>
@@ -3495,21 +3487,21 @@
         <v>37</v>
       </c>
       <c r="F100" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B101" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C101" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D101" t="s">
         <v>66</v>
@@ -3518,7 +3510,7 @@
         <v>34</v>
       </c>
       <c r="F101" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G101" s="1">
         <v>70</v>
@@ -3526,13 +3518,13 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B102" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C102" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D102" t="s">
         <v>66</v>
@@ -3541,21 +3533,21 @@
         <v>29</v>
       </c>
       <c r="F102" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B103" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C103" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D103" t="s">
         <v>66</v>
@@ -3564,30 +3556,30 @@
         <v>37</v>
       </c>
       <c r="F103" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B104" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C104" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D104" t="s">
         <v>66</v>
       </c>
       <c r="E104" t="s">
+        <v>176</v>
+      </c>
+      <c r="F104" t="s">
         <v>177</v>
-      </c>
-      <c r="F104" t="s">
-        <v>178</v>
       </c>
       <c r="G104" s="1">
         <v>70</v>
@@ -3595,13 +3587,13 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B105" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D105" t="s">
         <v>66</v>
@@ -3610,21 +3602,21 @@
         <v>29</v>
       </c>
       <c r="F105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B106" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C106" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D106" t="s">
         <v>66</v>
@@ -3633,30 +3625,30 @@
         <v>37</v>
       </c>
       <c r="F106" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B107" t="s">
+        <v>197</v>
+      </c>
+      <c r="C107" t="s">
+        <v>184</v>
+      </c>
+      <c r="D107" t="s">
         <v>198</v>
       </c>
-      <c r="C107" t="s">
+      <c r="E107" t="s">
+        <v>176</v>
+      </c>
+      <c r="F107" t="s">
         <v>185</v>
-      </c>
-      <c r="D107" t="s">
-        <v>199</v>
-      </c>
-      <c r="E107" t="s">
-        <v>177</v>
-      </c>
-      <c r="F107" t="s">
-        <v>186</v>
       </c>
       <c r="G107" s="1">
         <v>70</v>
@@ -3664,91 +3656,91 @@
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B108" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C108" t="s">
+        <v>187</v>
+      </c>
+      <c r="D108" t="s">
+        <v>198</v>
+      </c>
+      <c r="E108" t="s">
+        <v>29</v>
+      </c>
+      <c r="F108" t="s">
+        <v>185</v>
+      </c>
+      <c r="G108" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="D108" t="s">
-        <v>199</v>
-      </c>
-      <c r="E108" t="s">
-        <v>29</v>
-      </c>
-      <c r="F108" t="s">
-        <v>186</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B109" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C109" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D109" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E109" t="s">
         <v>37</v>
       </c>
       <c r="F109" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B110" t="s">
+        <v>201</v>
+      </c>
+      <c r="C110" t="s">
+        <v>170</v>
+      </c>
+      <c r="D110" t="s">
         <v>202</v>
       </c>
-      <c r="C110" t="s">
+      <c r="E110" t="s">
+        <v>29</v>
+      </c>
+      <c r="F110" t="s">
+        <v>168</v>
+      </c>
+      <c r="G110" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="D110" t="s">
-        <v>203</v>
-      </c>
-      <c r="E110" t="s">
-        <v>29</v>
-      </c>
-      <c r="F110" t="s">
-        <v>169</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B111" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C111" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D111" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E111" t="s">
         <v>34</v>
       </c>
       <c r="F111" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G111" s="1">
         <v>70</v>
@@ -3756,22 +3748,22 @@
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B112" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C112" t="s">
+        <v>175</v>
+      </c>
+      <c r="D112" t="s">
+        <v>127</v>
+      </c>
+      <c r="E112" t="s">
         <v>176</v>
       </c>
-      <c r="D112" t="s">
-        <v>128</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>177</v>
-      </c>
-      <c r="F112" t="s">
-        <v>178</v>
       </c>
       <c r="G112" s="1">
         <v>70</v>
@@ -3779,45 +3771,45 @@
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B113" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C113" t="s">
+        <v>179</v>
+      </c>
+      <c r="D113" t="s">
+        <v>127</v>
+      </c>
+      <c r="E113" t="s">
+        <v>29</v>
+      </c>
+      <c r="F113" t="s">
+        <v>177</v>
+      </c>
+      <c r="G113" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D113" t="s">
-        <v>128</v>
-      </c>
-      <c r="E113" t="s">
-        <v>29</v>
-      </c>
-      <c r="F113" t="s">
-        <v>178</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B114" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C114" t="s">
+        <v>184</v>
+      </c>
+      <c r="D114" t="s">
+        <v>127</v>
+      </c>
+      <c r="E114" t="s">
+        <v>176</v>
+      </c>
+      <c r="F114" t="s">
         <v>185</v>
-      </c>
-      <c r="D114" t="s">
-        <v>128</v>
-      </c>
-      <c r="E114" t="s">
-        <v>177</v>
-      </c>
-      <c r="F114" t="s">
-        <v>186</v>
       </c>
       <c r="G114" s="1">
         <v>70</v>
@@ -3825,68 +3817,68 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B115" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C115" t="s">
+        <v>187</v>
+      </c>
+      <c r="D115" t="s">
+        <v>127</v>
+      </c>
+      <c r="E115" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115" t="s">
+        <v>185</v>
+      </c>
+      <c r="G115" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="D115" t="s">
-        <v>128</v>
-      </c>
-      <c r="E115" t="s">
-        <v>29</v>
-      </c>
-      <c r="F115" t="s">
-        <v>186</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B116" t="s">
+        <v>208</v>
+      </c>
+      <c r="C116" t="s">
+        <v>187</v>
+      </c>
+      <c r="D116" t="s">
         <v>209</v>
       </c>
-      <c r="C116" t="s">
+      <c r="E116" t="s">
+        <v>29</v>
+      </c>
+      <c r="F116" t="s">
+        <v>185</v>
+      </c>
+      <c r="G116" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="D116" t="s">
-        <v>210</v>
-      </c>
-      <c r="E116" t="s">
-        <v>29</v>
-      </c>
-      <c r="F116" t="s">
-        <v>186</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B117" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C117" t="s">
+        <v>184</v>
+      </c>
+      <c r="D117" t="s">
+        <v>209</v>
+      </c>
+      <c r="E117" t="s">
+        <v>176</v>
+      </c>
+      <c r="F117" t="s">
         <v>185</v>
-      </c>
-      <c r="D117" t="s">
-        <v>210</v>
-      </c>
-      <c r="E117" t="s">
-        <v>177</v>
-      </c>
-      <c r="F117" t="s">
-        <v>186</v>
       </c>
       <c r="G117" s="1">
         <v>70</v>
@@ -3894,91 +3886,91 @@
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B118" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C118" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D118" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E118" t="s">
         <v>37</v>
       </c>
       <c r="F118" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B119" t="s">
+        <v>212</v>
+      </c>
+      <c r="C119" t="s">
+        <v>190</v>
+      </c>
+      <c r="D119" t="s">
         <v>213</v>
-      </c>
-      <c r="C119" t="s">
-        <v>191</v>
-      </c>
-      <c r="D119" t="s">
-        <v>214</v>
       </c>
       <c r="E119" t="s">
         <v>37</v>
       </c>
       <c r="F119" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B120" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C120" t="s">
+        <v>170</v>
+      </c>
+      <c r="D120" t="s">
+        <v>209</v>
+      </c>
+      <c r="E120" t="s">
+        <v>29</v>
+      </c>
+      <c r="F120" t="s">
+        <v>168</v>
+      </c>
+      <c r="G120" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="D120" t="s">
-        <v>210</v>
-      </c>
-      <c r="E120" t="s">
-        <v>29</v>
-      </c>
-      <c r="F120" t="s">
-        <v>169</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B121" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C121" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D121" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E121" t="s">
         <v>34</v>
       </c>
       <c r="F121" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G121" s="1">
         <v>70</v>
@@ -3986,91 +3978,91 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B122" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C122" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D122" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E122" t="s">
         <v>37</v>
       </c>
       <c r="F122" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B123" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C123" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D123" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E123" t="s">
         <v>37</v>
       </c>
       <c r="F123" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B124" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C124" t="s">
+        <v>179</v>
+      </c>
+      <c r="D124" t="s">
+        <v>209</v>
+      </c>
+      <c r="E124" t="s">
+        <v>29</v>
+      </c>
+      <c r="F124" t="s">
+        <v>177</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D124" t="s">
-        <v>210</v>
-      </c>
-      <c r="E124" t="s">
-        <v>29</v>
-      </c>
-      <c r="F124" t="s">
-        <v>178</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B125" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C125" t="s">
+        <v>175</v>
+      </c>
+      <c r="D125" t="s">
+        <v>209</v>
+      </c>
+      <c r="E125" t="s">
         <v>176</v>
       </c>
-      <c r="D125" t="s">
-        <v>210</v>
-      </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>177</v>
-      </c>
-      <c r="F125" t="s">
-        <v>178</v>
       </c>
       <c r="G125" s="1">
         <v>70</v>
@@ -4078,59 +4070,59 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B126" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C126" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D126" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E126" t="s">
         <v>37</v>
       </c>
       <c r="F126" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B127" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C127" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D127" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E127" t="s">
         <v>37</v>
       </c>
       <c r="F127" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B128" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C128" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D128" t="s">
         <v>83</v>
@@ -4139,21 +4131,21 @@
         <v>29</v>
       </c>
       <c r="F128" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C129" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D129" t="s">
         <v>83</v>
@@ -4162,7 +4154,7 @@
         <v>34</v>
       </c>
       <c r="F129" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G129" s="1">
         <v>70</v>
@@ -4170,68 +4162,68 @@
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B130" t="s">
+        <v>234</v>
+      </c>
+      <c r="C130" t="s">
         <v>235</v>
       </c>
-      <c r="C130" t="s">
-        <v>236</v>
-      </c>
       <c r="D130" t="s">
-        <v>237</v>
+        <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F130" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B131" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C131" t="s">
+        <v>179</v>
+      </c>
+      <c r="D131" t="s">
+        <v>224</v>
+      </c>
+      <c r="E131" t="s">
+        <v>29</v>
+      </c>
+      <c r="F131" t="s">
+        <v>177</v>
+      </c>
+      <c r="G131" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="D131" t="s">
-        <v>225</v>
-      </c>
-      <c r="E131" t="s">
-        <v>29</v>
-      </c>
-      <c r="F131" t="s">
-        <v>178</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B132" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C132" t="s">
+        <v>175</v>
+      </c>
+      <c r="D132" t="s">
+        <v>224</v>
+      </c>
+      <c r="E132" t="s">
         <v>176</v>
       </c>
-      <c r="D132" t="s">
-        <v>225</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>177</v>
-      </c>
-      <c r="F132" t="s">
-        <v>178</v>
       </c>
       <c r="G132" s="1">
         <v>70</v>
@@ -4239,68 +4231,68 @@
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B133" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C133" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D133" t="s">
-        <v>237</v>
+        <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F133" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B134" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C134" t="s">
+        <v>187</v>
+      </c>
+      <c r="D134" t="s">
+        <v>224</v>
+      </c>
+      <c r="E134" t="s">
+        <v>29</v>
+      </c>
+      <c r="F134" t="s">
+        <v>185</v>
+      </c>
+      <c r="G134" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="D134" t="s">
-        <v>225</v>
-      </c>
-      <c r="E134" t="s">
-        <v>29</v>
-      </c>
-      <c r="F134" t="s">
-        <v>186</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B135" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C135" t="s">
+        <v>184</v>
+      </c>
+      <c r="D135" t="s">
+        <v>224</v>
+      </c>
+      <c r="E135" t="s">
+        <v>176</v>
+      </c>
+      <c r="F135" t="s">
         <v>185</v>
-      </c>
-      <c r="D135" t="s">
-        <v>225</v>
-      </c>
-      <c r="E135" t="s">
-        <v>177</v>
-      </c>
-      <c r="F135" t="s">
-        <v>186</v>
       </c>
       <c r="G135" s="1">
         <v>70</v>
@@ -4308,36 +4300,36 @@
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B136" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C136" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D136" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E136" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F136" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B137" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C137" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D137" t="s">
         <v>83</v>
@@ -4346,21 +4338,21 @@
         <v>29</v>
       </c>
       <c r="F137" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B138" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C138" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D138" t="s">
         <v>83</v>
@@ -4369,7 +4361,7 @@
         <v>34</v>
       </c>
       <c r="F138" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G138" s="1">
         <v>70</v>
@@ -4377,13 +4369,13 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B139" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C139" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D139" t="s">
         <v>4</v>
@@ -4392,30 +4384,30 @@
         <v>29</v>
       </c>
       <c r="F139" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B140" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C140" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D140" t="s">
         <v>4</v>
       </c>
       <c r="E140" t="s">
+        <v>176</v>
+      </c>
+      <c r="F140" t="s">
         <v>177</v>
-      </c>
-      <c r="F140" t="s">
-        <v>178</v>
       </c>
       <c r="G140" s="1">
         <v>70</v>
@@ -4423,13 +4415,13 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B141" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C141" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D141" t="s">
         <v>4</v>
@@ -4438,36 +4430,37 @@
         <v>29</v>
       </c>
       <c r="F141" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B142" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C142" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D142" t="s">
         <v>4</v>
       </c>
       <c r="E142" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F142" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G142" s="1">
         <v>70</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G142" xr:uid="{278F8488-2E5D-430A-92BC-094A5D88171D}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -4478,7 +4471,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -4553,14 +4546,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>237</v>
-      </c>
-      <c r="B10" t="s">
-        <v>238</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/database.xlsx
+++ b/database.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawn.hsieh\Desktop\隔熱紙下單小幫手\KIA\資料拆開版\正式上線版\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawn.hsieh\Desktop\隔熱紙下單小幫手\KIA\資料拆開版\正式上線版\20261028更新\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94D8DEF0-EE36-4C0F-A209-B9723AF64128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046DC456-49F0-4778-BF71-F3F9CCB90B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1605" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="264">
   <si>
     <t>車型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -861,13 +861,6 @@
     <t>U5YH</t>
   </si>
   <si>
-    <t>8, 18, 38, 68</t>
-  </si>
-  <si>
-    <t>8, 18, 38, 68</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>隔熱紙-車身(KT系列,KT8,18,38,68)</t>
   </si>
   <si>
@@ -895,6 +888,10 @@
   </si>
   <si>
     <t>CD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>08, 18, 38, 68</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1343,7 +1340,7 @@
         <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D5" t="s">
         <v>27</v>
@@ -1355,7 +1352,7 @@
         <v>38</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1389,7 +1386,7 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D7" t="s">
         <v>27</v>
@@ -1401,7 +1398,7 @@
         <v>41</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1619,7 +1616,7 @@
         <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D17" t="s">
         <v>62</v>
@@ -1631,7 +1628,7 @@
         <v>38</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1665,7 +1662,7 @@
         <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D19" t="s">
         <v>62</v>
@@ -1677,7 +1674,7 @@
         <v>38</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1895,7 +1892,7 @@
         <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D29" t="s">
         <v>79</v>
@@ -1907,7 +1904,7 @@
         <v>38</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1941,7 +1938,7 @@
         <v>235</v>
       </c>
       <c r="C31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D31" t="s">
         <v>79</v>
@@ -1953,7 +1950,7 @@
         <v>38</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2171,7 +2168,7 @@
         <v>91</v>
       </c>
       <c r="C41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D41" t="s">
         <v>88</v>
@@ -2183,7 +2180,7 @@
         <v>38</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -2217,7 +2214,7 @@
         <v>93</v>
       </c>
       <c r="C43" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D43" t="s">
         <v>88</v>
@@ -2229,7 +2226,7 @@
         <v>38</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -2447,7 +2444,7 @@
         <v>108</v>
       </c>
       <c r="C53" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D53" t="s">
         <v>79</v>
@@ -2459,7 +2456,7 @@
         <v>109</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -2493,7 +2490,7 @@
         <v>241</v>
       </c>
       <c r="C55" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D55" t="s">
         <v>79</v>
@@ -2505,7 +2502,7 @@
         <v>109</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2588,7 +2585,7 @@
         <v>115</v>
       </c>
       <c r="D59" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E59" t="s">
         <v>28</v>
@@ -2611,7 +2608,7 @@
         <v>119</v>
       </c>
       <c r="D60" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E60" t="s">
         <v>33</v>
@@ -2634,7 +2631,7 @@
         <v>103</v>
       </c>
       <c r="D61" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E61" t="s">
         <v>28</v>
@@ -2657,7 +2654,7 @@
         <v>107</v>
       </c>
       <c r="D62" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E62" t="s">
         <v>33</v>
@@ -2677,10 +2674,10 @@
         <v>124</v>
       </c>
       <c r="C63" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E63" t="s">
         <v>28</v>
@@ -2689,7 +2686,7 @@
         <v>109</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -2703,7 +2700,7 @@
         <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E64" t="s">
         <v>33</v>
@@ -2861,7 +2858,7 @@
         <v>135</v>
       </c>
       <c r="C71" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D71" t="s">
         <v>127</v>
@@ -2873,7 +2870,7 @@
         <v>109</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -2907,7 +2904,7 @@
         <v>137</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D73" t="s">
         <v>127</v>
@@ -2919,7 +2916,7 @@
         <v>109</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -3068,7 +3065,7 @@
         <v>145</v>
       </c>
       <c r="C80" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D80" t="s">
         <v>139</v>
@@ -3080,7 +3077,7 @@
         <v>109</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -3114,7 +3111,7 @@
         <v>147</v>
       </c>
       <c r="C82" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D82" t="s">
         <v>139</v>
@@ -3126,7 +3123,7 @@
         <v>109</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -3275,7 +3272,7 @@
         <v>154</v>
       </c>
       <c r="C89" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D89" t="s">
         <v>62</v>
@@ -3287,7 +3284,7 @@
         <v>109</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -3321,7 +3318,7 @@
         <v>156</v>
       </c>
       <c r="C91" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D91" t="s">
         <v>62</v>
@@ -3333,7 +3330,7 @@
         <v>109</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -3807,7 +3804,7 @@
         <v>167</v>
       </c>
       <c r="D112" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E112" t="s">
         <v>168</v>
@@ -3830,7 +3827,7 @@
         <v>171</v>
       </c>
       <c r="D113" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E113" t="s">
         <v>28</v>
@@ -3853,7 +3850,7 @@
         <v>176</v>
       </c>
       <c r="D114" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E114" t="s">
         <v>168</v>
@@ -3876,7 +3873,7 @@
         <v>179</v>
       </c>
       <c r="D115" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E115" t="s">
         <v>28</v>
@@ -4520,7 +4517,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
